--- a/informes_data/Primera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486370_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Primera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486370_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>3.4533</v>
+        <v>3.5844</v>
       </c>
       <c r="E2" t="n">
-        <v>5.3736</v>
+        <v>5.5971</v>
       </c>
       <c r="F2" t="n">
-        <v>-1.9203</v>
+        <v>-2.0128</v>
       </c>
       <c r="G2" t="n">
         <v>2.1795</v>
@@ -610,13 +610,13 @@
         <v>0.435</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.2912</v>
+        <v>-0.1601</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.3425</v>
+        <v>-0.119</v>
       </c>
       <c r="U2" t="n">
-        <v>0.0513</v>
+        <v>-0.0412</v>
       </c>
       <c r="V2" t="n">
         <v>1.13</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.2507</v>
+        <v>3.0112</v>
       </c>
       <c r="E3" t="n">
-        <v>3.3592</v>
+        <v>4.4588</v>
       </c>
       <c r="F3" t="n">
-        <v>-1.1085</v>
+        <v>-1.4476</v>
       </c>
       <c r="G3" t="n">
         <v>1.1413</v>
@@ -688,13 +688,13 @@
         <v>2.1751</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.9951</v>
+        <v>-0.2346</v>
       </c>
       <c r="T3" t="n">
-        <v>-1.0839</v>
+        <v>0.0156</v>
       </c>
       <c r="U3" t="n">
-        <v>0.0888</v>
+        <v>-0.2503</v>
       </c>
       <c r="V3" t="n">
         <v>1.017</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.4653</v>
+        <v>2.2237</v>
       </c>
       <c r="E4" t="n">
-        <v>3.0168</v>
+        <v>3.8676</v>
       </c>
       <c r="F4" t="n">
-        <v>-1.5515</v>
+        <v>-1.644</v>
       </c>
       <c r="G4" t="n">
         <v>-0.9727</v>
@@ -766,13 +766,13 @@
         <v>0.435</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.4522</v>
+        <v>0.3061</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.548</v>
+        <v>0.3028</v>
       </c>
       <c r="U4" t="n">
-        <v>0.0958</v>
+        <v>0.0033</v>
       </c>
       <c r="V4" t="n">
         <v>2.4552</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.8472</v>
+        <v>0.3183</v>
       </c>
       <c r="E5" t="n">
-        <v>1.7863</v>
+        <v>1.0725</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.9391</v>
+        <v>-0.7541</v>
       </c>
       <c r="G5" t="n">
         <v>-0.4802</v>
@@ -844,13 +844,13 @@
         <v>0.435</v>
       </c>
       <c r="S5" t="n">
-        <v>0.8924</v>
+        <v>0.3635</v>
       </c>
       <c r="T5" t="n">
-        <v>1.2161</v>
+        <v>0.5023</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.3237</v>
+        <v>-0.1388</v>
       </c>
       <c r="V5" t="n">
         <v>0</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.2972</v>
+        <v>0.0325</v>
       </c>
       <c r="E6" t="n">
-        <v>1.198</v>
+        <v>1.5585</v>
       </c>
       <c r="F6" t="n">
-        <v>-1.4952</v>
+        <v>-1.526</v>
       </c>
       <c r="G6" t="n">
         <v>-0.0574</v>
@@ -922,13 +922,13 @@
         <v>0.435</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.4796</v>
+        <v>-0.1499</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.411</v>
+        <v>-0.0505</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.06859999999999999</v>
+        <v>-0.0994</v>
       </c>
       <c r="V6" t="n">
         <v>-0.1952</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>R. GILL</t>
+          <t>K. SMITH</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,58 +955,58 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.4884</v>
+        <v>-0.6838</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.6961</v>
+        <v>0.5089</v>
       </c>
       <c r="F7" t="n">
-        <v>1.2077</v>
+        <v>-1.1927</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.379</v>
+        <v>-1.9877</v>
       </c>
       <c r="H7" t="n">
-        <v>-1.1161</v>
+        <v>-3.23</v>
       </c>
       <c r="I7" t="n">
-        <v>0.7371</v>
+        <v>1.2423</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.4067</v>
+        <v>0.3935</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.4832</v>
+        <v>-2.0162</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0765</v>
+        <v>2.4097</v>
       </c>
       <c r="M7" t="n">
-        <v>0.0277</v>
+        <v>-2.3812</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.6328</v>
+        <v>-1.2138</v>
       </c>
       <c r="O7" t="n">
-        <v>0.6606</v>
+        <v>-1.1674</v>
       </c>
       <c r="P7" t="n">
-        <v>-0.435</v>
+        <v>1.9576</v>
       </c>
       <c r="Q7" t="n">
-        <v>-2.1751</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>1.7401</v>
+        <v>1.9576</v>
       </c>
       <c r="S7" t="n">
-        <v>0.6338</v>
+        <v>-0.3455</v>
       </c>
       <c r="T7" t="n">
-        <v>0.8857</v>
+        <v>0.1154</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.2519</v>
+        <v>-0.4609</v>
       </c>
       <c r="V7" t="n">
         <v>-0.3082</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>C. OKANU</t>
+          <t>R. GILL</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.6405999999999999</v>
+        <v>-0.8302</v>
       </c>
       <c r="E8" t="n">
-        <v>3.2592</v>
+        <v>-2.1612</v>
       </c>
       <c r="F8" t="n">
-        <v>-3.8997</v>
+        <v>1.331</v>
       </c>
       <c r="G8" t="n">
-        <v>-3.4071</v>
+        <v>-0.379</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.3312</v>
+        <v>-1.1161</v>
       </c>
       <c r="I8" t="n">
-        <v>-3.0759</v>
+        <v>0.7371</v>
       </c>
       <c r="J8" t="n">
-        <v>0.9686</v>
+        <v>-0.4067</v>
       </c>
       <c r="K8" t="n">
-        <v>0.8156</v>
+        <v>-0.4832</v>
       </c>
       <c r="L8" t="n">
-        <v>0.153</v>
+        <v>0.0765</v>
       </c>
       <c r="M8" t="n">
-        <v>-4.3757</v>
+        <v>0.0277</v>
       </c>
       <c r="N8" t="n">
-        <v>-1.1468</v>
+        <v>-0.6328</v>
       </c>
       <c r="O8" t="n">
-        <v>-3.2289</v>
+        <v>0.6606</v>
       </c>
       <c r="P8" t="n">
-        <v>0.87</v>
+        <v>-0.435</v>
       </c>
       <c r="Q8" t="n">
+        <v>-2.1751</v>
+      </c>
+      <c r="R8" t="n">
+        <v>1.7401</v>
+      </c>
+      <c r="S8" t="n">
+        <v>0.292</v>
+      </c>
+      <c r="T8" t="n">
+        <v>0.4206</v>
+      </c>
+      <c r="U8" t="n">
+        <v>-0.1286</v>
+      </c>
+      <c r="V8" t="n">
+        <v>-0.3082</v>
+      </c>
+      <c r="W8" t="n">
         <v>0</v>
       </c>
-      <c r="R8" t="n">
-        <v>0.87</v>
-      </c>
-      <c r="S8" t="n">
-        <v>2.4408</v>
-      </c>
-      <c r="T8" t="n">
-        <v>2.8348</v>
-      </c>
-      <c r="U8" t="n">
-        <v>-0.394</v>
-      </c>
-      <c r="V8" t="n">
-        <v>-0.5443</v>
-      </c>
-      <c r="W8" t="n">
-        <v>-0.5443</v>
-      </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>-0.3082</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>K. SMITH</t>
+          <t>S. MC DONNELL</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.8709</v>
+        <v>-1.1621</v>
       </c>
       <c r="E9" t="n">
-        <v>0.2602</v>
+        <v>-0.5649999999999999</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.1311</v>
+        <v>-0.5971</v>
       </c>
       <c r="G9" t="n">
-        <v>-1.9877</v>
+        <v>-0.8608</v>
       </c>
       <c r="H9" t="n">
-        <v>-3.23</v>
+        <v>-1.1772</v>
       </c>
       <c r="I9" t="n">
-        <v>1.2423</v>
+        <v>0.3163</v>
       </c>
       <c r="J9" t="n">
-        <v>0.3935</v>
+        <v>0.0414</v>
       </c>
       <c r="K9" t="n">
-        <v>-2.0162</v>
+        <v>0.0032</v>
       </c>
       <c r="L9" t="n">
-        <v>2.4097</v>
+        <v>0.0382</v>
       </c>
       <c r="M9" t="n">
-        <v>-2.3812</v>
+        <v>-0.9022</v>
       </c>
       <c r="N9" t="n">
-        <v>-1.2138</v>
+        <v>-1.1803</v>
       </c>
       <c r="O9" t="n">
-        <v>-1.1674</v>
+        <v>0.2781</v>
       </c>
       <c r="P9" t="n">
-        <v>1.9576</v>
+        <v>-0.2175</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>-2.1751</v>
       </c>
       <c r="R9" t="n">
         <v>1.9576</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.5326</v>
+        <v>0.2244</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.1334</v>
+        <v>0.4386</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.3992</v>
+        <v>-0.2142</v>
       </c>
       <c r="V9" t="n">
         <v>-0.3082</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X9" t="n">
-        <v>-0.3082</v>
+        <v>-1.4382</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>S. MC DONNELL</t>
+          <t>C. OKANU</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.198</v>
+        <v>-2.4412</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.3235</v>
+        <v>1.4278</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.8745000000000001</v>
+        <v>-3.8689</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.8608</v>
+        <v>-3.4071</v>
       </c>
       <c r="H10" t="n">
-        <v>-1.1772</v>
+        <v>-0.3312</v>
       </c>
       <c r="I10" t="n">
-        <v>0.3163</v>
+        <v>-3.0759</v>
       </c>
       <c r="J10" t="n">
-        <v>0.0414</v>
+        <v>0.9686</v>
       </c>
       <c r="K10" t="n">
-        <v>0.0032</v>
+        <v>0.8156</v>
       </c>
       <c r="L10" t="n">
-        <v>0.0382</v>
+        <v>0.153</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.9022</v>
+        <v>-4.3757</v>
       </c>
       <c r="N10" t="n">
-        <v>-1.1803</v>
+        <v>-1.1468</v>
       </c>
       <c r="O10" t="n">
-        <v>0.2781</v>
+        <v>-3.2289</v>
       </c>
       <c r="P10" t="n">
-        <v>-0.2175</v>
+        <v>0.87</v>
       </c>
       <c r="Q10" t="n">
-        <v>-2.1751</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>1.9576</v>
+        <v>0.87</v>
       </c>
       <c r="S10" t="n">
-        <v>0.1886</v>
+        <v>0.6402</v>
       </c>
       <c r="T10" t="n">
-        <v>0.6802</v>
+        <v>1.0034</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.4916</v>
+        <v>-0.3632</v>
       </c>
       <c r="V10" t="n">
-        <v>-0.3082</v>
+        <v>-0.5443</v>
       </c>
       <c r="W10" t="n">
-        <v>1.13</v>
+        <v>-0.5443</v>
       </c>
       <c r="X10" t="n">
-        <v>-1.4382</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-5.9116</v>
+        <v>-5.265</v>
       </c>
       <c r="E11" t="n">
-        <v>-4.6874</v>
+        <v>-3.9484</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.2242</v>
+        <v>-1.3167</v>
       </c>
       <c r="G11" t="n">
         <v>-6.8222</v>
@@ -1312,13 +1312,13 @@
         <v>1.305</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.8067</v>
+        <v>-0.1601</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.6044</v>
+        <v>0.1346</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.2023</v>
+        <v>-0.2947</v>
       </c>
       <c r="V11" t="n">
         <v>1.4997</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-7.07</v>
+        <v>-5.878</v>
       </c>
       <c r="E12" t="n">
-        <v>-5.6816</v>
+        <v>-4.5821</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.3883</v>
+        <v>-1.2959</v>
       </c>
       <c r="G12" t="n">
         <v>-8.271599999999999</v>
@@ -1390,13 +1390,13 @@
         <v>1.305</v>
       </c>
       <c r="S12" t="n">
-        <v>-1.1629</v>
+        <v>0.0291</v>
       </c>
       <c r="T12" t="n">
-        <v>-1.0274</v>
+        <v>0.0721</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.1354</v>
+        <v>-0.043</v>
       </c>
       <c r="V12" t="n">
         <v>2.1469</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-8.4602</v>
+        <v>-7.0902</v>
       </c>
       <c r="E13" t="n">
-        <v>5.864699999999998</v>
+        <v>7.234500000000003</v>
       </c>
       <c r="F13" t="n">
-        <v>-14.3247</v>
+        <v>-14.3248</v>
       </c>
       <c r="G13" t="n">
         <v>-19.9179</v>
@@ -1444,10 +1444,10 @@
         <v>2.734799999999999</v>
       </c>
       <c r="K13" t="n">
-        <v>-0.5444000000000004</v>
+        <v>-0.5443999999999996</v>
       </c>
       <c r="L13" t="n">
-        <v>3.2791</v>
+        <v>3.279100000000001</v>
       </c>
       <c r="M13" t="n">
         <v>-22.6524</v>
@@ -1468,13 +1468,13 @@
         <v>13.0504</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.5647000000000004</v>
+        <v>0.8050999999999999</v>
       </c>
       <c r="T13" t="n">
-        <v>1.4662</v>
+        <v>2.8359</v>
       </c>
       <c r="U13" t="n">
-        <v>-2.0308</v>
+        <v>-2.031</v>
       </c>
       <c r="V13" t="n">
         <v>6.5847</v>
@@ -1483,7 +1483,7 @@
         <v>9.2765</v>
       </c>
       <c r="X13" t="n">
-        <v>-2.691599999999999</v>
+        <v>-2.6916</v>
       </c>
     </row>
     <row r="14">
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>7.0725</v>
+        <v>6.8219</v>
       </c>
       <c r="E14" t="n">
-        <v>9.6515</v>
+        <v>9.092700000000001</v>
       </c>
       <c r="F14" t="n">
-        <v>-2.579</v>
+        <v>-2.2708</v>
       </c>
       <c r="G14" t="n">
         <v>7.1011</v>
@@ -1546,13 +1546,13 @@
         <v>0.87</v>
       </c>
       <c r="S14" t="n">
-        <v>0.0361</v>
+        <v>-0.2145</v>
       </c>
       <c r="T14" t="n">
-        <v>0.8736</v>
+        <v>0.3149</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.8376</v>
+        <v>-0.5294</v>
       </c>
       <c r="V14" t="n">
         <v>-0.9347</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>4.7931</v>
+        <v>4.612</v>
       </c>
       <c r="E15" t="n">
-        <v>3.9405</v>
+        <v>3.6053</v>
       </c>
       <c r="F15" t="n">
-        <v>0.8526</v>
+        <v>1.0067</v>
       </c>
       <c r="G15" t="n">
         <v>3.5191</v>
@@ -1624,13 +1624,13 @@
         <v>0.87</v>
       </c>
       <c r="S15" t="n">
-        <v>1.1218</v>
+        <v>0.9406</v>
       </c>
       <c r="T15" t="n">
-        <v>0.8051</v>
+        <v>0.4699</v>
       </c>
       <c r="U15" t="n">
-        <v>0.3166</v>
+        <v>0.4708</v>
       </c>
       <c r="V15" t="n">
         <v>0.3698</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>3.4134</v>
+        <v>2.9548</v>
       </c>
       <c r="E16" t="n">
-        <v>5.1408</v>
+        <v>4.8055</v>
       </c>
       <c r="F16" t="n">
-        <v>-1.7274</v>
+        <v>-1.8507</v>
       </c>
       <c r="G16" t="n">
         <v>3.8683</v>
@@ -1702,13 +1702,13 @@
         <v>1.305</v>
       </c>
       <c r="S16" t="n">
-        <v>0.3047</v>
+        <v>-0.1538</v>
       </c>
       <c r="T16" t="n">
-        <v>0.5997</v>
+        <v>0.2644</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.2949</v>
+        <v>-0.4182</v>
       </c>
       <c r="V16" t="n">
         <v>-2.0647</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>G. KORSANTIA</t>
+          <t>T. MCGHIE</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,67 +1735,67 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>1.588</v>
+        <v>1.2801</v>
       </c>
       <c r="E17" t="n">
-        <v>1.9922</v>
+        <v>-0.0824</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.4042</v>
+        <v>1.3625</v>
       </c>
       <c r="G17" t="n">
-        <v>0.8018999999999999</v>
+        <v>0.26</v>
       </c>
       <c r="H17" t="n">
-        <v>1.3111</v>
+        <v>-1.4995</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.5092</v>
+        <v>1.7595</v>
       </c>
       <c r="J17" t="n">
-        <v>1.9527</v>
+        <v>-0.3662</v>
       </c>
       <c r="K17" t="n">
-        <v>1.7614</v>
+        <v>-1.3806</v>
       </c>
       <c r="L17" t="n">
-        <v>0.1912</v>
+        <v>1.0144</v>
       </c>
       <c r="M17" t="n">
-        <v>-1.1508</v>
+        <v>0.6262</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.4504</v>
+        <v>-0.1188</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.7004</v>
+        <v>0.7451</v>
       </c>
       <c r="P17" t="n">
-        <v>-1.5225</v>
+        <v>0.87</v>
       </c>
       <c r="Q17" t="n">
-        <v>-2.1751</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>0.6525</v>
+        <v>0.87</v>
       </c>
       <c r="S17" t="n">
-        <v>2.3087</v>
+        <v>-0.4149</v>
       </c>
       <c r="T17" t="n">
-        <v>1.8242</v>
+        <v>-0.2812</v>
       </c>
       <c r="U17" t="n">
-        <v>0.4845</v>
+        <v>-0.1337</v>
       </c>
       <c r="V17" t="n">
-        <v>-0</v>
+        <v>0.5649999999999999</v>
       </c>
       <c r="W17" t="n">
-        <v>0.3904</v>
+        <v>0.5649999999999999</v>
       </c>
       <c r="X17" t="n">
-        <v>-0.3904</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>1.0939</v>
+        <v>1.0001</v>
       </c>
       <c r="E18" t="n">
-        <v>1.9155</v>
+        <v>1.5803</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.8217</v>
+        <v>-0.5802</v>
       </c>
       <c r="G18" t="n">
         <v>1.8129</v>
@@ -1858,13 +1858,13 @@
         <v>0.6525</v>
       </c>
       <c r="S18" t="n">
-        <v>0.0857</v>
+        <v>-0.0081</v>
       </c>
       <c r="T18" t="n">
-        <v>0.8051</v>
+        <v>0.4699</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.7195</v>
+        <v>-0.478</v>
       </c>
       <c r="V18" t="n">
         <v>-0.3698</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>T. MCGHIE</t>
+          <t>G. KORSANTIA</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,67 +1891,67 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.6417</v>
+        <v>0.4846</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.4177</v>
+        <v>0.9864000000000001</v>
       </c>
       <c r="F19" t="n">
-        <v>1.0594</v>
+        <v>-0.5018</v>
       </c>
       <c r="G19" t="n">
-        <v>0.26</v>
+        <v>0.8018999999999999</v>
       </c>
       <c r="H19" t="n">
-        <v>-1.4995</v>
+        <v>1.3111</v>
       </c>
       <c r="I19" t="n">
-        <v>1.7595</v>
+        <v>-0.5092</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.3662</v>
+        <v>1.9527</v>
       </c>
       <c r="K19" t="n">
-        <v>-1.3806</v>
+        <v>1.7614</v>
       </c>
       <c r="L19" t="n">
-        <v>1.0144</v>
+        <v>0.1912</v>
       </c>
       <c r="M19" t="n">
-        <v>0.6262</v>
+        <v>-1.1508</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.1188</v>
+        <v>-0.4504</v>
       </c>
       <c r="O19" t="n">
-        <v>0.7451</v>
+        <v>-0.7004</v>
       </c>
       <c r="P19" t="n">
-        <v>0.87</v>
+        <v>-1.5225</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>-2.1751</v>
       </c>
       <c r="R19" t="n">
-        <v>0.87</v>
+        <v>0.6525</v>
       </c>
       <c r="S19" t="n">
-        <v>-1.0533</v>
+        <v>1.2053</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.6165</v>
+        <v>0.8184</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.4368</v>
+        <v>0.3869</v>
       </c>
       <c r="V19" t="n">
-        <v>0.5649999999999999</v>
+        <v>-0</v>
       </c>
       <c r="W19" t="n">
-        <v>0.5649999999999999</v>
+        <v>0.3904</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>-0.3904</v>
       </c>
     </row>
     <row r="20">
@@ -1969,10 +1969,10 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.4909</v>
+        <v>-0.0438</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.632</v>
+        <v>-1.185</v>
       </c>
       <c r="F20" t="n">
         <v>1.1412</v>
@@ -2014,10 +2014,10 @@
         <v>0.87</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.7691</v>
+        <v>-0.3221</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.6165</v>
+        <v>-0.1694</v>
       </c>
       <c r="U20" t="n">
         <v>-0.1526</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.1937</v>
+        <v>-1.6175</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.8446</v>
+        <v>-1.6211</v>
       </c>
       <c r="F21" t="n">
-        <v>0.6509</v>
+        <v>0.0036</v>
       </c>
       <c r="G21" t="n">
         <v>0.9692</v>
@@ -2092,13 +2092,13 @@
         <v>0.435</v>
       </c>
       <c r="S21" t="n">
-        <v>0.9023</v>
+        <v>0.4786</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.4795</v>
+        <v>-0.256</v>
       </c>
       <c r="U21" t="n">
-        <v>1.3818</v>
+        <v>0.7345</v>
       </c>
       <c r="V21" t="n">
         <v>-1.3252</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-3.7181</v>
+        <v>-2.4786</v>
       </c>
       <c r="E22" t="n">
-        <v>-2.0196</v>
+        <v>-1.2373</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.6985</v>
+        <v>-1.2413</v>
       </c>
       <c r="G22" t="n">
         <v>-0.1988</v>
@@ -2170,13 +2170,13 @@
         <v>0.6525</v>
       </c>
       <c r="S22" t="n">
-        <v>-1.2365</v>
+        <v>0.003</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.6165</v>
+        <v>0.1658</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.6201</v>
+        <v>-0.1628</v>
       </c>
       <c r="V22" t="n">
         <v>-0.7602</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-4.7398</v>
+        <v>-3.8085</v>
       </c>
       <c r="E23" t="n">
-        <v>-2.402</v>
+        <v>-1.6197</v>
       </c>
       <c r="F23" t="n">
-        <v>-2.3378</v>
+        <v>-2.1888</v>
       </c>
       <c r="G23" t="n">
         <v>-0.6917</v>
@@ -2248,13 +2248,13 @@
         <v>0.435</v>
       </c>
       <c r="S23" t="n">
-        <v>-1.1356</v>
+        <v>-0.2043</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.548</v>
+        <v>0.2343</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.5876</v>
+        <v>-0.4386</v>
       </c>
       <c r="V23" t="n">
         <v>-2.2599</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>8.460100000000001</v>
+        <v>9.2051</v>
       </c>
       <c r="E24" t="n">
-        <v>14.3246</v>
+        <v>14.3247</v>
       </c>
       <c r="F24" t="n">
-        <v>-5.864500000000001</v>
+        <v>-5.1196</v>
       </c>
       <c r="G24" t="n">
         <v>19.9176</v>
@@ -2323,16 +2323,16 @@
         <v>-13.0504</v>
       </c>
       <c r="R24" t="n">
-        <v>7.612499999999999</v>
+        <v>7.6125</v>
       </c>
       <c r="S24" t="n">
-        <v>0.5648000000000002</v>
+        <v>1.3098</v>
       </c>
       <c r="T24" t="n">
-        <v>2.0307</v>
+        <v>2.031</v>
       </c>
       <c r="U24" t="n">
-        <v>-1.4662</v>
+        <v>-0.7210999999999999</v>
       </c>
       <c r="V24" t="n">
         <v>-6.5845</v>
